--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R487b7dd6f4ba4870"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3bf604b95a2847eb"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3bf604b95a2847eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R49c78df803014af8"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R49c78df803014af8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R767254e9b78c48cf"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R767254e9b78c48cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3af6d262c14841e5"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3af6d262c14841e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R42657b3db55c4b31"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R42657b3db55c4b31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbe98eb21991e47d8"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbe98eb21991e47d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R78f51f8822134c3f"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R78f51f8822134c3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rec754a5196b542f1"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rec754a5196b542f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5af9944f92844eaf"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5af9944f92844eaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfbe5bc49c6a741f4"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfbe5bc49c6a741f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbc204053a0b64e87"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbc204053a0b64e87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R33532e0054a7438d"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R33532e0054a7438d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2625cc90cef94143"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2625cc90cef94143"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc899a32dadd44658"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupPrintArea/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc899a32dadd44658"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2ea791f675e64980"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$1,'Sheet1'!$A$3:$A$3</x:definedName>
